--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1291,7 +1291,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
     </row>
     <row r="183">
       <c r="A183" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
     </row>
     <row r="186">
       <c r="A186" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
     </row>
     <row r="200">
       <c r="A200" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
     </row>
     <row r="203">
       <c r="A203" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
     </row>
     <row r="205">
       <c r="A205" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
     </row>
     <row r="207">
       <c r="A207" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
     </row>
     <row r="225">
       <c r="A225" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
     </row>
     <row r="227">
       <c r="A227" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -5191,7 +5191,7 @@
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -5191,7 +5191,7 @@
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1291,7 +1291,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1993,7 +1993,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -2149,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -2149,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
     </row>
     <row r="186">
       <c r="A186" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1993,7 +1993,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="98">
       <c r="A98" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
     </row>
     <row r="227">
       <c r="A227" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1993,7 +1993,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>

--- a/etf_monitoraggio.xlsx
+++ b/etf_monitoraggio.xlsx
@@ -1993,7 +1993,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
